--- a/Document/PSFB/PFSB.xlsx
+++ b/Document/PSFB/PFSB.xlsx
@@ -1,25 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\PSFB\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F10107-09A3-476B-BCAE-5B93A5341180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -66,6 +87,1099 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>549480</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>19567</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{805E24BD-366D-478D-A288-9D74A03E9F74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9693480" cy="3311407"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>71</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>10450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>569393</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>14082</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E78C8A66-2E57-11A4-EB95-D21DB26BA3A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219271" y="3642110"/>
+          <a:ext cx="1178922" cy="3632"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>570412</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>178525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>574766</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>8708</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CCA354E-71A9-817D-2623-9DA1542DD8F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2399212" y="3653245"/>
+          <a:ext cx="4354" cy="195943"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>570411</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>184484</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>40105</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>184484</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Straight Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{387EBDDE-7862-9448-5698-119CF46CBD7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2399211" y="3874168"/>
+          <a:ext cx="1298494" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>16042</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>4011</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>8021</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21862106-5798-6DA8-FB80-652D6C7CB57B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1235242" y="3878179"/>
+          <a:ext cx="1203158" cy="4010"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>20053</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Straight Connector 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8534D6CF-C9EC-AD4F-2BDE-E571E2F3A167}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2438400" y="3689684"/>
+          <a:ext cx="0" cy="204537"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3243</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>176463</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>12032</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9727</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Straight Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54B1483D-3253-7F23-0FC8-F0CCE0A8544F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2441643" y="3626540"/>
+          <a:ext cx="1227989" cy="14847"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>44116</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>176463</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>48126</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>4011</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="Straight Connector 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AD8EBA1-F380-16D4-AA16-011D00198369}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3701716" y="3681663"/>
+          <a:ext cx="4010" cy="196516"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>6656</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>161189</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>6656</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>8789</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="Straight Connector 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0716107-DAAA-3123-AA57-03FC2B85AFBC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3664256" y="3611266"/>
+          <a:ext cx="0" cy="210766"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38910</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>175098</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>376136</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>178340</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="Straight Connector 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{820C4551-5167-A1AA-4F22-BE0F07BF87BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3696510" y="3625175"/>
+          <a:ext cx="946826" cy="3242"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>16213</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>178340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>327498</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>181582</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="Straight Connector 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4019371-32DB-54A9-F890-BC5571F44C2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3673813" y="3810000"/>
+          <a:ext cx="920885" cy="3242"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>599873</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>559595</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>3632</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="Straight Connector 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEAFA439-88AA-4895-8FBD-24F9F12183A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1819073" y="3994826"/>
+          <a:ext cx="1178922" cy="3632"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>593558</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>4010</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="Straight Connector 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A22D3D51-002E-45CE-A11E-813B869ACE9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4176409"/>
+          <a:ext cx="1203158" cy="4010"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>593388</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>178340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>596630</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>178938</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="Straight Connector 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEBB7BFC-C190-4600-8F2F-B8EF899ACDB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3031788" y="3991583"/>
+          <a:ext cx="3242" cy="182181"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>547714</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>180470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552068</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>10653</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="36" name="Straight Connector 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD0027F2-0824-4767-AA02-C8D6AC259CA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2986114" y="3993713"/>
+          <a:ext cx="4354" cy="193349"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>547992</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>178340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>55123</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>3242</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="Straight Connector 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FF06A33-2202-4BDD-BDD9-654F172E1121}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2986392" y="4173166"/>
+          <a:ext cx="1335931" cy="6485"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>596630</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>176975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3243</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>3242</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="39" name="Straight Connector 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{550C47BD-A355-43B9-AE74-00D63D4DC59C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3035030" y="3990218"/>
+          <a:ext cx="1235413" cy="7850"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>606357</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>3242</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="41" name="Straight Connector 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21499955-9F7B-4D90-B8EF-662D8AFFF32C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4263957" y="3994826"/>
+          <a:ext cx="3243" cy="184825"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>55124</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>175098</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>59134</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>2646</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="44" name="Straight Connector 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E707C545-A12D-49CE-824B-CAB08D618054}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4322324" y="3988341"/>
+          <a:ext cx="4010" cy="190714"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>603115</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9727</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>12969</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="Straight Connector 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35826561-677B-4DE5-96E0-F96966C18890}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4260715" y="4186136"/>
+          <a:ext cx="920885" cy="3242"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>64851</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>178340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>402077</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>181582</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="46" name="Straight Connector 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC4F3E40-E445-48BE-9434-ABA420537806}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4332051" y="3991583"/>
+          <a:ext cx="946826" cy="3242"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>10886</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>95132</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>97570</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Picture 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B1BC408-B7BB-8B60-9FD4-8BEF0CA39E68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9764486" y="0"/>
+          <a:ext cx="7399446" cy="5834341"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +1444,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Document/PSFB/PFSB.xlsx
+++ b/Document/PSFB/PFSB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\PSFB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F10107-09A3-476B-BCAE-5B93A5341180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8DF967-BA06-48A3-A6D0-11AC5152E951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,15 +36,134 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>Mode1 Q1Q4导通</t>
+  </si>
+  <si>
+    <t>原边Q1Q4导通电流路径为Vin-&gt;Lr-&gt;Q4-&gt;GND 副边导通电流路径为D1-&gt;Lout-&gt;D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仅Q4导通，电容电感谐振结束C1、C2充放电完成后，原边电流靠Lr续流，续流路径为Lr→Q4→Dq2
+→Lr，此时无能量传输给副边，副边电流由Lout续流。由于Dq2导通，此时Q2的Vds被钳位至0V。
+</t>
+  </si>
+  <si>
+    <t>MODE 4: Q2/Q4导通Q2导通时，由于其被寄生二极管钳位至0V，故Q2的导通为ZVS。此时续流路径为
+Lr→Q4→Q2→Lr。原边电压依旧为0V，副边靠Lout续流。</t>
+  </si>
+  <si>
+    <t>Q4关断，仅Q2导通，此时C4开始充电，充电电流路径为Lr→C4→Q2→Lr。同时由于Q3源极电位被拉高，C3开始放电，放电电流路径为C3→电源→Q2→Lr→C3。由于C4和C3充放电的影响，Q4的Vds不会发生突变，即Q4关断过程中Vds近似为0V，故Q4的关断为ZVS。</t>
+  </si>
+  <si>
+    <t>C4、C3充放电完成后，C4电压升至电源电压，原边电流继续靠Lr续流，续流路径为Lr→Dq3→电源→Q2→Lr
+。由于Dq3导通，此时Q3的Vds被钳位为0</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>https://techweb.rohm.com/product/transistors-diodes/transistors/9769/</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/712760404</t>
+  </si>
+  <si>
+    <t>Mode2：仅Q4导通
+电容电感谐振</t>
+  </si>
+  <si>
+    <t>Mode3：仅Q4导通
+电容电感谐振结束</t>
+  </si>
+  <si>
+    <t>Mode4：Q2Q4导通</t>
+  </si>
+  <si>
+    <t>Mode5：仅Q2导通
+电容电感谐振</t>
+  </si>
+  <si>
+    <t>Mode6:仅Q2导通
+电容电感谐振结束</t>
+  </si>
+  <si>
+    <t>Mode7：Q2Q3导通
+原边电流迅速衰减</t>
+  </si>
+  <si>
+    <t>Q3导通时，由于其Vds被寄生二极管钳位至0V，故Q3的导通为ZVS。由于Q3的导通，电源电压Vin反向加在Lr两端，原边电流迅速减小至0A。</t>
+  </si>
+  <si>
+    <t>Q2、Q3导通，电流路径为电源正→Q3→Lr→Q2→电源负。此时C1和C4充电至电源电压 Vin，D1、D4电流降为0A，D2、D3和变压器副边构成回路，原边和副边电流分别流过Lr和Lout，电能开始在电感中储存。原边电流Ip线性增加，能量从电源通过变压器传递给负载。</t>
+  </si>
+  <si>
+    <t>Mode8：Q2Q3导通
+原边电流反向增加</t>
+  </si>
+  <si>
+    <t>电容电感谐振</t>
+  </si>
+  <si>
+    <t>Mode9：仅Q4导通</t>
+  </si>
+  <si>
+    <t>Q2关断，仅Q3导通，此时C2开始充电，充电电流路径为电源正→Q3→Lr→C2→电源负。同时由于Q1源极电位被拉高，C1开始放电，放电电流路径为C1→Q3→Lr→C1。由于C2和C1充放电的影响，Q2的Vds不会发生突变，即Q2关断过程中Vds
+近似为0V，故Q2的关断为ZVS。</t>
+  </si>
+  <si>
+    <t>MODE 10: 仅Q3导通，
+电容电感谐振结束</t>
+  </si>
+  <si>
+    <t>C2、C1充放电完成后，原边电流靠续流，续流路径为Lr→Dq1→Q3→Lr，此时无能量传输给副边，副边电流由续流。由于Dq1导通，此时Q1的Vds被钳位至0V。</t>
+  </si>
+  <si>
+    <t>MODE 11: Q1/Q3导通</t>
+  </si>
+  <si>
+    <t>Q1导通时，由于其Vds被寄生二极管钳位至0V，故Q1的导通为ZVS。此时续流路径为Lr→Q1→Q3→Lr。原边电压依旧为0V，副边靠Lout续流。</t>
+  </si>
+  <si>
+    <t>MODE 12: 仅Q1导通，电容电感谐振</t>
+  </si>
+  <si>
+    <t>Q3关断，仅Q1导通，此时C3开始充电，充电电流路径为Lr→Q1→C3→Lr。同时由于Q4漏极电位被拉低，C4开始放电，放电电流路径为C4→Lr→Q1→电源→C4。由于C3和C4充放电的影响，Q3的Vds不会发生突变，即Q3关断过程中Vds近似为0V，故Q3的关断为ZVS。与MODE 5类似，此时Lr储存的能量用于支持电容电感的谐振，所以MODE 12开始时刻Lr内部必须存有足够的能量。变压器原边电压此时会从0V增加为Vc3，正向感应电动势导致副边D1、D4导通，此时变压器副边被短路。</t>
+  </si>
+  <si>
+    <t>MODE 13: 仅Q1导通，电容电感谐振结束</t>
+  </si>
+  <si>
+    <t>C3、C4充放电完成后，C3电压升至电源电压Vin，原边电流继续靠Lr续流，续流路径为Lr→Q1→电源→Qd4→Lr。由于Qd4
+导通，此时Q4的Vds被钳位至0V</t>
+  </si>
+  <si>
+    <t>MODE 14: Q1/Q4导通，原边电流迅速衰减</t>
+  </si>
+  <si>
+    <t>Q4导通时，由于其Vds被寄生二极管钳位至0V，故Q4的导通为ZVS。由于Q4的导通，电源电压Vin
+正向加在Lr两端，原边电流迅速减小至0A。</t>
+  </si>
+  <si>
+    <t>Q1关断，仅Q4导通，此时C1开始充电，充电电流路径为电源正→C1→→Q4→电源负。同时由于Q2漏极电位被拉低，C2开始放电，放电电流路径为C2→Lr→Q4→C2。由于C1和C2充放电的影响，Q1的Vds不会发生突变，即Q1关断过程中Vds近似为0V，故Q1关断软开关</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -67,13 +186,38 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -99,7 +243,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>549480</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>19567</xdr:rowOff>
@@ -1171,6 +1315,714 @@
         <a:xfrm>
           <a:off x="9764486" y="0"/>
           <a:ext cx="7399446" cy="5834341"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>99390</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>72887</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>364435</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>42725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A51E5BF-E9A8-BCC4-EB63-C67FC15A1F48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="99390" y="4896678"/>
+          <a:ext cx="6970645" cy="3680447"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>496956</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>26505</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>582847</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>178905</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ECB8E68-B131-4ACE-DA2B-03D5FE12827D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="496956" y="9528314"/>
+          <a:ext cx="7401091" cy="3863008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>689113</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>99392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>247801</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>115003</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8661CE1-671F-B1BD-E136-81C3D0E67DCA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="689113" y="14279218"/>
+          <a:ext cx="7483488" cy="4282811"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>649357</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>169942</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>124935</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D0BACB0-5979-F991-2C40-0871B8783DAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="649357" y="19613217"/>
+          <a:ext cx="7445385" cy="4206605"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>244495</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>145157</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E279C853-E398-0102-F523-8CDFCA91BD64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="25191720"/>
+          <a:ext cx="7559695" cy="4351397"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>221632</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>145151</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A0E5FE6-39F4-DFCE-96DF-0EA084050986}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1234440" y="31432500"/>
+          <a:ext cx="7521592" cy="4282811"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>419770</xdr:colOff>
+      <xdr:row>242</xdr:row>
+      <xdr:rowOff>168003</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0394339-22D4-F41E-4555-4E15F04F851D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="36850320"/>
+          <a:ext cx="7734970" cy="4191363"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>250</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>236874</xdr:colOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>107054</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{500059AC-4809-EE90-08A9-EE75BC2DCEA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="42336720"/>
+          <a:ext cx="7552074" cy="4313294"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>277</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>206392</xdr:colOff>
+      <xdr:row>300</xdr:row>
+      <xdr:rowOff>61330</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AEEF400-03B5-293E-BE9F-879506DFCEF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="47640240"/>
+          <a:ext cx="7521592" cy="4267570"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>304</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>587412</xdr:colOff>
+      <xdr:row>326</xdr:row>
+      <xdr:rowOff>152762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84853FE9-8D95-DE34-5606-CD75C39E567C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="762000" y="52852320"/>
+          <a:ext cx="7750212" cy="4176122"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>883920</xdr:colOff>
+      <xdr:row>332</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>518815</xdr:colOff>
+      <xdr:row>356</xdr:row>
+      <xdr:rowOff>168022</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4827513E-E779-007C-6FD3-2324D6591E62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="883920" y="58491120"/>
+          <a:ext cx="7559695" cy="4404742"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>678180</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>579798</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>53713</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91E5A9D2-1730-0A5C-3083-ADBC976331A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="678180" y="25100280"/>
+          <a:ext cx="7826418" cy="4305673"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1188720</xdr:colOff>
+      <xdr:row>364</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>385</xdr:row>
+      <xdr:rowOff>30363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DFF879D-5653-27F4-63F7-7BC61E776565}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1188720" y="68671440"/>
+          <a:ext cx="6766560" cy="3779403"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>392</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>358805</xdr:colOff>
+      <xdr:row>414</xdr:row>
+      <xdr:rowOff>145141</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8476D46B-827A-EA32-2D3A-C3839790DC5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="74066400"/>
+          <a:ext cx="7674005" cy="4168501"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1027" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82550A9F-6D97-CFDC-C7F5-E52A964FDFAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9753600" y="10507980"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>13646</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>26504</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>14967</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57EF3B99-FD43-4CC7-A2E9-7598A101CF7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10363200" y="6321681"/>
+          <a:ext cx="10999304" cy="4897999"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1445,10 +2297,1026 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A19:O392"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+    </row>
+    <row r="73" spans="1:11" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+    </row>
+    <row r="100" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="7"/>
+      <c r="K100" s="7"/>
+      <c r="L100" s="7"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="7"/>
+    </row>
+    <row r="102" spans="1:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B102" s="7"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="7"/>
+    </row>
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="7"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="7"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="7"/>
+    </row>
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="7"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7"/>
+      <c r="J104" s="7"/>
+      <c r="K104" s="7"/>
+      <c r="L104" s="7"/>
+    </row>
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="7"/>
+    </row>
+    <row r="131" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
+      <c r="G131" s="7"/>
+      <c r="H131" s="7"/>
+      <c r="I131" s="7"/>
+      <c r="J131" s="7"/>
+      <c r="K131" s="7"/>
+      <c r="L131" s="7"/>
+      <c r="M131" s="7"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="7"/>
+      <c r="J132" s="7"/>
+      <c r="K132" s="7"/>
+      <c r="L132" s="7"/>
+      <c r="M132" s="7"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="7"/>
+      <c r="H133" s="7"/>
+      <c r="I133" s="7"/>
+      <c r="J133" s="7"/>
+      <c r="K133" s="7"/>
+      <c r="L133" s="7"/>
+      <c r="M133" s="7"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B134" s="7"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
+      <c r="I134" s="7"/>
+      <c r="J134" s="7"/>
+      <c r="K134" s="7"/>
+      <c r="L134" s="7"/>
+      <c r="M134" s="7"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B135" s="7"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
+      <c r="G135" s="7"/>
+      <c r="H135" s="7"/>
+      <c r="I135" s="7"/>
+      <c r="J135" s="7"/>
+      <c r="K135" s="7"/>
+      <c r="L135" s="7"/>
+      <c r="M135" s="7"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B136" s="7"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="7"/>
+      <c r="J136" s="7"/>
+      <c r="K136" s="7"/>
+      <c r="L136" s="7"/>
+      <c r="M136" s="7"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="7"/>
+      <c r="H137" s="7"/>
+      <c r="I137" s="7"/>
+      <c r="J137" s="7"/>
+      <c r="K137" s="7"/>
+      <c r="L137" s="7"/>
+      <c r="M137" s="7"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B138" s="7"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="7"/>
+      <c r="K138" s="7"/>
+      <c r="L138" s="7"/>
+      <c r="M138" s="7"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B139" s="7"/>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
+      <c r="G139" s="7"/>
+      <c r="H139" s="7"/>
+      <c r="I139" s="7"/>
+      <c r="J139" s="7"/>
+      <c r="K139" s="7"/>
+      <c r="L139" s="7"/>
+      <c r="M139" s="7"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B140" s="7"/>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="7"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
+      <c r="I140" s="7"/>
+      <c r="J140" s="7"/>
+      <c r="K140" s="7"/>
+      <c r="L140" s="7"/>
+      <c r="M140" s="7"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B141" s="7"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+      <c r="G141" s="7"/>
+      <c r="H141" s="7"/>
+      <c r="I141" s="7"/>
+      <c r="J141" s="7"/>
+      <c r="K141" s="7"/>
+      <c r="L141" s="7"/>
+      <c r="M141" s="7"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B142" s="7"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="7"/>
+      <c r="H142" s="7"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="7"/>
+      <c r="K142" s="7"/>
+      <c r="L142" s="7"/>
+      <c r="M142" s="7"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B143" s="7"/>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
+      <c r="H143" s="7"/>
+      <c r="I143" s="7"/>
+      <c r="J143" s="7"/>
+      <c r="K143" s="7"/>
+      <c r="L143" s="7"/>
+      <c r="M143" s="7"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B144" s="7"/>
+      <c r="C144" s="7"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="7"/>
+      <c r="G144" s="7"/>
+      <c r="H144" s="7"/>
+      <c r="I144" s="7"/>
+      <c r="J144" s="7"/>
+      <c r="K144" s="7"/>
+      <c r="L144" s="7"/>
+      <c r="M144" s="7"/>
+    </row>
+    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
+      <c r="I145" s="7"/>
+      <c r="J145" s="7"/>
+      <c r="K145" s="7"/>
+      <c r="L145" s="7"/>
+      <c r="M145" s="7"/>
+    </row>
+    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="7"/>
+      <c r="K146" s="7"/>
+      <c r="L146" s="7"/>
+      <c r="M146" s="7"/>
+    </row>
+    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B147" s="7"/>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="7"/>
+      <c r="K147" s="7"/>
+      <c r="L147" s="7"/>
+      <c r="M147" s="7"/>
+    </row>
+    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B148" s="7"/>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="7"/>
+      <c r="K148" s="7"/>
+      <c r="L148" s="7"/>
+      <c r="M148" s="7"/>
+    </row>
+    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
+      <c r="I149" s="7"/>
+      <c r="J149" s="7"/>
+      <c r="K149" s="7"/>
+      <c r="L149" s="7"/>
+      <c r="M149" s="7"/>
+    </row>
+    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B150" s="7"/>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7"/>
+      <c r="G150" s="7"/>
+      <c r="H150" s="7"/>
+      <c r="I150" s="7"/>
+      <c r="J150" s="7"/>
+      <c r="K150" s="7"/>
+      <c r="L150" s="7"/>
+      <c r="M150" s="7"/>
+    </row>
+    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B151" s="7"/>
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
+      <c r="I151" s="7"/>
+      <c r="J151" s="7"/>
+      <c r="K151" s="7"/>
+      <c r="L151" s="7"/>
+      <c r="M151" s="7"/>
+    </row>
+    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B152" s="7"/>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
+      <c r="I152" s="7"/>
+      <c r="J152" s="7"/>
+      <c r="K152" s="7"/>
+      <c r="L152" s="7"/>
+      <c r="M152" s="7"/>
+    </row>
+    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
+      <c r="I153" s="7"/>
+      <c r="J153" s="7"/>
+      <c r="K153" s="7"/>
+      <c r="L153" s="7"/>
+      <c r="M153" s="7"/>
+    </row>
+    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B154" s="7"/>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
+      <c r="G154" s="7"/>
+      <c r="H154" s="7"/>
+      <c r="I154" s="7"/>
+      <c r="J154" s="7"/>
+      <c r="K154" s="7"/>
+      <c r="L154" s="7"/>
+      <c r="M154" s="7"/>
+    </row>
+    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B155" s="7"/>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+      <c r="I155" s="7"/>
+      <c r="J155" s="7"/>
+      <c r="K155" s="7"/>
+      <c r="L155" s="7"/>
+      <c r="M155" s="7"/>
+    </row>
+    <row r="156" spans="2:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B156" s="7"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+      <c r="I156" s="7"/>
+      <c r="J156" s="7"/>
+      <c r="K156" s="7"/>
+      <c r="L156" s="7"/>
+      <c r="M156" s="7"/>
+    </row>
+    <row r="157" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="7"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="7"/>
+      <c r="K157" s="7"/>
+      <c r="L157" s="7"/>
+      <c r="M157" s="7"/>
+    </row>
+    <row r="158" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B158" s="7"/>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
+      <c r="G158" s="7"/>
+      <c r="H158" s="7"/>
+      <c r="I158" s="7"/>
+      <c r="J158" s="7"/>
+      <c r="K158" s="7"/>
+      <c r="L158" s="7"/>
+      <c r="M158" s="7"/>
+    </row>
+    <row r="159" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B159" s="7"/>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
+      <c r="I159" s="7"/>
+      <c r="J159" s="7"/>
+      <c r="K159" s="7"/>
+      <c r="L159" s="7"/>
+      <c r="M159" s="7"/>
+    </row>
+    <row r="160" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B160" s="7"/>
+      <c r="C160" s="7"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="7"/>
+      <c r="K160" s="7"/>
+      <c r="L160" s="7"/>
+      <c r="M160" s="7"/>
+    </row>
+    <row r="162" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
+      <c r="G162" s="7"/>
+      <c r="H162" s="7"/>
+      <c r="I162" s="7"/>
+      <c r="J162" s="7"/>
+      <c r="K162" s="7"/>
+      <c r="L162" s="7"/>
+      <c r="M162" s="7"/>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B163" s="7"/>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="7"/>
+      <c r="H163" s="7"/>
+      <c r="I163" s="7"/>
+      <c r="J163" s="7"/>
+      <c r="K163" s="7"/>
+      <c r="L163" s="7"/>
+      <c r="M163" s="7"/>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B164" s="7"/>
+      <c r="C164" s="7"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="7"/>
+      <c r="H164" s="7"/>
+      <c r="I164" s="7"/>
+      <c r="J164" s="7"/>
+      <c r="K164" s="7"/>
+      <c r="L164" s="7"/>
+      <c r="M164" s="7"/>
+    </row>
+    <row r="189" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C189" s="7"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
+      <c r="I189" s="7"/>
+      <c r="J189" s="7"/>
+      <c r="K189" s="7"/>
+      <c r="L189" s="7"/>
+      <c r="M189" s="7"/>
+    </row>
+    <row r="217" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A217" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C217" s="7"/>
+      <c r="D217" s="7"/>
+      <c r="E217" s="7"/>
+      <c r="F217" s="7"/>
+      <c r="G217" s="7"/>
+      <c r="H217" s="7"/>
+      <c r="I217" s="7"/>
+      <c r="J217" s="7"/>
+      <c r="K217" s="7"/>
+      <c r="L217" s="7"/>
+      <c r="M217" s="7"/>
+      <c r="N217" s="7"/>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B218" s="7"/>
+      <c r="C218" s="7"/>
+      <c r="D218" s="7"/>
+      <c r="E218" s="7"/>
+      <c r="F218" s="7"/>
+      <c r="G218" s="7"/>
+      <c r="H218" s="7"/>
+      <c r="I218" s="7"/>
+      <c r="J218" s="7"/>
+      <c r="K218" s="7"/>
+      <c r="L218" s="7"/>
+      <c r="M218" s="7"/>
+      <c r="N218" s="7"/>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B219" s="7"/>
+      <c r="C219" s="7"/>
+      <c r="D219" s="7"/>
+      <c r="E219" s="7"/>
+      <c r="F219" s="7"/>
+      <c r="G219" s="7"/>
+      <c r="H219" s="7"/>
+      <c r="I219" s="7"/>
+      <c r="J219" s="7"/>
+      <c r="K219" s="7"/>
+      <c r="L219" s="7"/>
+      <c r="M219" s="7"/>
+      <c r="N219" s="7"/>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B220" s="7"/>
+      <c r="C220" s="7"/>
+      <c r="D220" s="7"/>
+      <c r="E220" s="7"/>
+      <c r="F220" s="7"/>
+      <c r="G220" s="7"/>
+      <c r="H220" s="7"/>
+      <c r="I220" s="7"/>
+      <c r="J220" s="7"/>
+      <c r="K220" s="7"/>
+      <c r="L220" s="7"/>
+      <c r="M220" s="7"/>
+      <c r="N220" s="7"/>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>19</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C245" s="7"/>
+      <c r="D245" s="7"/>
+      <c r="E245" s="7"/>
+      <c r="F245" s="7"/>
+      <c r="G245" s="7"/>
+      <c r="H245" s="7"/>
+      <c r="I245" s="7"/>
+      <c r="J245" s="7"/>
+      <c r="K245" s="7"/>
+      <c r="L245" s="7"/>
+      <c r="M245" s="7"/>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>18</v>
+      </c>
+      <c r="B246" s="7"/>
+      <c r="C246" s="7"/>
+      <c r="D246" s="7"/>
+      <c r="E246" s="7"/>
+      <c r="F246" s="7"/>
+      <c r="G246" s="7"/>
+      <c r="H246" s="7"/>
+      <c r="I246" s="7"/>
+      <c r="J246" s="7"/>
+      <c r="K246" s="7"/>
+      <c r="L246" s="7"/>
+      <c r="M246" s="7"/>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B247" s="7"/>
+      <c r="C247" s="7"/>
+      <c r="D247" s="7"/>
+      <c r="E247" s="7"/>
+      <c r="F247" s="7"/>
+      <c r="G247" s="7"/>
+      <c r="H247" s="7"/>
+      <c r="I247" s="7"/>
+      <c r="J247" s="7"/>
+      <c r="K247" s="7"/>
+      <c r="L247" s="7"/>
+      <c r="M247" s="7"/>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B248" s="7"/>
+      <c r="C248" s="7"/>
+      <c r="D248" s="7"/>
+      <c r="E248" s="7"/>
+      <c r="F248" s="7"/>
+      <c r="G248" s="7"/>
+      <c r="H248" s="7"/>
+      <c r="I248" s="7"/>
+      <c r="J248" s="7"/>
+      <c r="K248" s="7"/>
+      <c r="L248" s="7"/>
+      <c r="M248" s="7"/>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B249" s="7"/>
+      <c r="C249" s="7"/>
+      <c r="D249" s="7"/>
+      <c r="E249" s="7"/>
+      <c r="F249" s="7"/>
+      <c r="G249" s="7"/>
+      <c r="H249" s="7"/>
+      <c r="I249" s="7"/>
+      <c r="J249" s="7"/>
+      <c r="K249" s="7"/>
+      <c r="L249" s="7"/>
+      <c r="M249" s="7"/>
+    </row>
+    <row r="276" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A276" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C276" s="7"/>
+      <c r="D276" s="7"/>
+      <c r="E276" s="7"/>
+      <c r="F276" s="7"/>
+      <c r="G276" s="7"/>
+      <c r="H276" s="7"/>
+      <c r="I276" s="7"/>
+      <c r="J276" s="7"/>
+      <c r="K276" s="7"/>
+      <c r="L276" s="7"/>
+      <c r="M276" s="7"/>
+    </row>
+    <row r="303" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A303" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C303" s="7"/>
+      <c r="D303" s="7"/>
+      <c r="E303" s="7"/>
+      <c r="F303" s="7"/>
+      <c r="G303" s="7"/>
+      <c r="H303" s="7"/>
+      <c r="I303" s="7"/>
+      <c r="J303" s="7"/>
+      <c r="K303" s="7"/>
+      <c r="L303" s="7"/>
+      <c r="M303" s="7"/>
+    </row>
+    <row r="329" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A329" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C329" s="9"/>
+      <c r="D329" s="9"/>
+      <c r="E329" s="9"/>
+      <c r="F329" s="9"/>
+      <c r="G329" s="9"/>
+      <c r="H329" s="9"/>
+      <c r="I329" s="9"/>
+      <c r="J329" s="9"/>
+      <c r="K329" s="9"/>
+      <c r="L329" s="9"/>
+      <c r="M329" s="9"/>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B330" s="9"/>
+      <c r="C330" s="9"/>
+      <c r="D330" s="9"/>
+      <c r="E330" s="9"/>
+      <c r="F330" s="9"/>
+      <c r="G330" s="9"/>
+      <c r="H330" s="9"/>
+      <c r="I330" s="9"/>
+      <c r="J330" s="9"/>
+      <c r="K330" s="9"/>
+      <c r="L330" s="9"/>
+      <c r="M330" s="9"/>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B331" s="9"/>
+      <c r="C331" s="9"/>
+      <c r="D331" s="9"/>
+      <c r="E331" s="9"/>
+      <c r="F331" s="9"/>
+      <c r="G331" s="9"/>
+      <c r="H331" s="9"/>
+      <c r="I331" s="9"/>
+      <c r="J331" s="9"/>
+      <c r="K331" s="9"/>
+      <c r="L331" s="9"/>
+      <c r="M331" s="9"/>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B332" s="9"/>
+      <c r="C332" s="9"/>
+      <c r="D332" s="9"/>
+      <c r="E332" s="9"/>
+      <c r="F332" s="9"/>
+      <c r="G332" s="9"/>
+      <c r="H332" s="9"/>
+      <c r="I332" s="9"/>
+      <c r="J332" s="9"/>
+      <c r="K332" s="9"/>
+      <c r="L332" s="9"/>
+      <c r="M332" s="9"/>
+    </row>
+    <row r="360" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A360" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C360" s="7"/>
+      <c r="D360" s="7"/>
+      <c r="E360" s="7"/>
+      <c r="F360" s="7"/>
+      <c r="G360" s="7"/>
+      <c r="H360" s="7"/>
+      <c r="I360" s="7"/>
+      <c r="J360" s="7"/>
+      <c r="K360" s="7"/>
+      <c r="L360" s="7"/>
+      <c r="M360" s="7"/>
+    </row>
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B361" s="7"/>
+      <c r="C361" s="7"/>
+      <c r="D361" s="7"/>
+      <c r="E361" s="7"/>
+      <c r="F361" s="7"/>
+      <c r="G361" s="7"/>
+      <c r="H361" s="7"/>
+      <c r="I361" s="7"/>
+      <c r="J361" s="7"/>
+      <c r="K361" s="7"/>
+      <c r="L361" s="7"/>
+      <c r="M361" s="7"/>
+    </row>
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B362" s="7"/>
+      <c r="C362" s="7"/>
+      <c r="D362" s="7"/>
+      <c r="E362" s="7"/>
+      <c r="F362" s="7"/>
+      <c r="G362" s="7"/>
+      <c r="H362" s="7"/>
+      <c r="I362" s="7"/>
+      <c r="J362" s="7"/>
+      <c r="K362" s="7"/>
+      <c r="L362" s="7"/>
+      <c r="M362" s="7"/>
+    </row>
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B363" s="7"/>
+      <c r="C363" s="7"/>
+      <c r="D363" s="7"/>
+      <c r="E363" s="7"/>
+      <c r="F363" s="7"/>
+      <c r="G363" s="7"/>
+      <c r="H363" s="7"/>
+      <c r="I363" s="7"/>
+      <c r="J363" s="7"/>
+      <c r="K363" s="7"/>
+      <c r="L363" s="7"/>
+      <c r="M363" s="7"/>
+    </row>
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B364" s="7"/>
+      <c r="C364" s="7"/>
+      <c r="D364" s="7"/>
+      <c r="E364" s="7"/>
+      <c r="F364" s="7"/>
+      <c r="G364" s="7"/>
+      <c r="H364" s="7"/>
+      <c r="I364" s="7"/>
+      <c r="J364" s="7"/>
+      <c r="K364" s="7"/>
+      <c r="L364" s="7"/>
+      <c r="M364" s="7"/>
+    </row>
+    <row r="390" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A390" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B390" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C390" s="7"/>
+      <c r="D390" s="7"/>
+      <c r="E390" s="7"/>
+      <c r="F390" s="7"/>
+      <c r="G390" s="7"/>
+      <c r="H390" s="7"/>
+      <c r="I390" s="7"/>
+      <c r="J390" s="7"/>
+      <c r="K390" s="7"/>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B391" s="7"/>
+      <c r="C391" s="7"/>
+      <c r="D391" s="7"/>
+      <c r="E391" s="7"/>
+      <c r="F391" s="7"/>
+      <c r="G391" s="7"/>
+      <c r="H391" s="7"/>
+      <c r="I391" s="7"/>
+      <c r="J391" s="7"/>
+      <c r="K391" s="7"/>
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B392" s="7"/>
+      <c r="C392" s="7"/>
+      <c r="D392" s="7"/>
+      <c r="E392" s="7"/>
+      <c r="F392" s="7"/>
+      <c r="G392" s="7"/>
+      <c r="H392" s="7"/>
+      <c r="I392" s="7"/>
+      <c r="J392" s="7"/>
+      <c r="K392" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B189:M189"/>
+    <mergeCell ref="B49:O49"/>
+    <mergeCell ref="B73:K73"/>
+    <mergeCell ref="B100:L105"/>
+    <mergeCell ref="B131:M160"/>
+    <mergeCell ref="B162:M164"/>
+    <mergeCell ref="B360:M364"/>
+    <mergeCell ref="B390:K392"/>
+    <mergeCell ref="B217:N220"/>
+    <mergeCell ref="B245:M249"/>
+    <mergeCell ref="B276:M276"/>
+    <mergeCell ref="B303:M303"/>
+    <mergeCell ref="B329:M332"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A20" r:id="rId1" xr:uid="{8F9EC5F7-5D51-4BC0-A17E-3138430B2EF4}"/>
+    <hyperlink ref="A21" r:id="rId2" xr:uid="{0C80D7F5-FA6D-40B7-BD3C-C328FD0F6D4A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>